--- a/气象/表格文件/比冷权重.xlsx
+++ b/气象/表格文件/比冷权重.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF34E064-8C12-4D32-8376-E579013B4149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16793CC4-193F-4845-9CDA-5CCA4BD5E51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{61358E34-2C71-424E-88ED-402A34315EC4}"/>
   </bookViews>
@@ -236,10 +236,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>漠河</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>图里河</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -344,7 +340,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>常年使用 1997-2020</t>
+    <t>卡丘格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常年使用 1991-2020</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -525,20 +525,19 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FFFF00FF"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color rgb="FF3F37C9"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -717,53 +716,53 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1107,32 +1106,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="29"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="28"/>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="32"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="31"/>
       <c r="E2" s="16" t="s">
         <v>26</v>
       </c>
       <c r="F2" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="H2" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="17" t="s">
         <v>23</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
@@ -1149,17 +1148,17 @@
         <v>3</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" s="20">
         <f xml:space="preserve"> B4*H4 + B5*H5 + B6*H6 + B7*H7 + B8*H8 + B9*H9 + B10*H10 + B11*H11</f>
-        <v>0.42499999999999977</v>
+        <v>-0.8350000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
@@ -1176,14 +1175,14 @@
         <v>9</v>
       </c>
       <c r="F4" s="21">
-        <v>-28.4</v>
+        <v>-28.2</v>
       </c>
       <c r="G4" s="22">
-        <v>-28</v>
+        <v>-27.9</v>
       </c>
       <c r="H4" s="24">
         <f>G4-F4</f>
-        <v>0.39999999999999858</v>
+        <v>0.30000000000000071</v>
       </c>
       <c r="I4" s="23"/>
     </row>
@@ -1200,21 +1199,21 @@
       <c r="E5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="21">
-        <v>-45.3</v>
-      </c>
-      <c r="G5" s="22">
-        <v>-43.3</v>
+      <c r="F5" s="25">
+        <v>-44.8</v>
+      </c>
+      <c r="G5" s="21">
+        <v>-45.1</v>
       </c>
       <c r="H5" s="24">
         <f t="shared" ref="H5:H11" si="0">G5-F5</f>
-        <v>2</v>
+        <v>-0.30000000000000426</v>
       </c>
       <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="14">
         <v>0.15</v>
@@ -1223,17 +1222,17 @@
         <v>0</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="21">
+        <v>19</v>
+      </c>
+      <c r="F6" s="25">
         <v>-36</v>
       </c>
-      <c r="G6" s="26">
-        <v>-35.1</v>
+      <c r="G6" s="21">
+        <v>-36.299999999999997</v>
       </c>
       <c r="H6" s="24">
         <f t="shared" si="0"/>
-        <v>0.89999999999999858</v>
+        <v>-0.29999999999999716</v>
       </c>
       <c r="I6" s="23"/>
     </row>
@@ -1250,15 +1249,15 @@
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="26">
-        <v>-26</v>
+      <c r="F7" s="21">
+        <v>-25.7</v>
       </c>
       <c r="G7" s="22">
-        <v>-26</v>
+        <v>-25.4</v>
       </c>
       <c r="H7" s="24">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30000000000000071</v>
       </c>
       <c r="I7" s="23"/>
     </row>
@@ -1276,20 +1275,20 @@
         <v>12</v>
       </c>
       <c r="F8" s="22">
-        <v>-27.6</v>
+        <v>-27.2</v>
       </c>
       <c r="G8" s="21">
-        <v>-28.1</v>
+        <v>-36.6</v>
       </c>
       <c r="H8" s="24">
         <f t="shared" si="0"/>
-        <v>-0.5</v>
+        <v>-9.4000000000000021</v>
       </c>
       <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="15">
         <v>0.05</v>
@@ -1298,17 +1297,17 @@
         <v>15</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="26">
+        <v>18</v>
+      </c>
+      <c r="F9" s="21">
         <v>-3.3</v>
       </c>
-      <c r="G9" s="25">
-        <v>-4.5999999999999996</v>
+      <c r="G9" s="32">
+        <v>-0.7</v>
       </c>
       <c r="H9" s="24">
         <f t="shared" si="0"/>
-        <v>-1.2999999999999998</v>
+        <v>2.5999999999999996</v>
       </c>
       <c r="I9" s="23"/>
     </row>
@@ -1329,11 +1328,11 @@
         <v>-50.2</v>
       </c>
       <c r="G10" s="21">
-        <v>-52.3</v>
+        <v>-51.5</v>
       </c>
       <c r="H10" s="24">
         <f t="shared" si="0"/>
-        <v>-2.0999999999999943</v>
+        <v>-1.2999999999999972</v>
       </c>
       <c r="I10" s="23"/>
     </row>
@@ -1354,11 +1353,11 @@
         <v>-3.7</v>
       </c>
       <c r="G11" s="22">
-        <v>-3.5</v>
+        <v>-3.2</v>
       </c>
       <c r="H11" s="24">
         <f t="shared" si="0"/>
-        <v>0.20000000000000018</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="23"/>
     </row>

--- a/气象/表格文件/比冷权重.xlsx
+++ b/气象/表格文件/比冷权重.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16793CC4-193F-4845-9CDA-5CCA4BD5E51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D80A994-CFA0-409B-8409-59611A64D0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{61358E34-2C71-424E-88ED-402A34315EC4}"/>
   </bookViews>
@@ -332,19 +332,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A的领先幅度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>卡丘格</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>常年使用 1991-2020</t>
+    <t>A的
+单项领先</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A的加权
+综合领先</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>常年:
+1961-1990</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -352,10 +355,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,15 +449,6 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="16"/>
       <name val="等线"/>
       <family val="3"/>
@@ -508,6 +503,69 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color rgb="FFFF00FF"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF3F37C9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF3F37C9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FFFF00FF"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
       <color theme="1" tint="0.499984740745262"/>
       <name val="等线"/>
       <family val="3"/>
@@ -516,31 +574,30 @@
     </font>
     <font>
       <b/>
+      <sz val="24"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="16"/>
-      <color rgb="FFFF00FF"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FF3F37C9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -559,6 +616,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -664,7 +727,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -695,11 +758,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="176" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
@@ -710,39 +776,9 @@
     <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -761,8 +797,44 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="177" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="177" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1100,39 +1172,44 @@
     <col min="3" max="3" width="14.59765625" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.06640625" style="1"/>
     <col min="5" max="7" width="24.59765625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.06640625" style="1"/>
-    <col min="9" max="9" width="16.59765625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.59765625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.59765625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="28"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="19"/>
+      <c r="E1" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="31"/>
-      <c r="E2" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>23</v>
-      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="34"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
@@ -1144,21 +1221,21 @@
       <c r="C3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="19" t="s">
+      <c r="G3" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="32">
         <f xml:space="preserve"> B4*H4 + B5*H5 + B6*H6 + B7*H7 + B8*H8 + B9*H9 + B10*H10 + B11*H11</f>
-        <v>-0.8350000000000003</v>
+        <v>-0.4199999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
@@ -1174,17 +1251,17 @@
       <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="21">
-        <v>-28.2</v>
-      </c>
-      <c r="G4" s="22">
-        <v>-27.9</v>
-      </c>
-      <c r="H4" s="24">
+      <c r="F4" s="27">
+        <v>-29.4</v>
+      </c>
+      <c r="G4" s="28">
+        <v>-28.4</v>
+      </c>
+      <c r="H4" s="31">
         <f>G4-F4</f>
-        <v>0.30000000000000071</v>
-      </c>
-      <c r="I4" s="23"/>
+        <v>1</v>
+      </c>
+      <c r="I4" s="16"/>
     </row>
     <row r="5" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
@@ -1199,17 +1276,17 @@
       <c r="E5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="29">
         <v>-44.8</v>
       </c>
-      <c r="G5" s="21">
-        <v>-45.1</v>
-      </c>
-      <c r="H5" s="24">
+      <c r="G5" s="27">
+        <v>-44.5</v>
+      </c>
+      <c r="H5" s="31">
         <f t="shared" ref="H5:H11" si="0">G5-F5</f>
-        <v>-0.30000000000000426</v>
-      </c>
-      <c r="I5" s="23"/>
+        <v>0.29999999999999716</v>
+      </c>
+      <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
@@ -1224,17 +1301,17 @@
       <c r="E6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="29">
         <v>-36</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="27">
         <v>-36.299999999999997</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="31">
         <f t="shared" si="0"/>
         <v>-0.29999999999999716</v>
       </c>
-      <c r="I6" s="23"/>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
@@ -1249,17 +1326,17 @@
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="21">
-        <v>-25.7</v>
-      </c>
-      <c r="G7" s="22">
-        <v>-25.4</v>
-      </c>
-      <c r="H7" s="24">
+      <c r="F7" s="27">
+        <v>-27.1</v>
+      </c>
+      <c r="G7" s="28">
+        <v>-26</v>
+      </c>
+      <c r="H7" s="31">
         <f t="shared" si="0"/>
-        <v>0.30000000000000071</v>
-      </c>
-      <c r="I7" s="23"/>
+        <v>1.1000000000000014</v>
+      </c>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
@@ -1274,17 +1351,17 @@
       <c r="E8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="22">
-        <v>-27.2</v>
-      </c>
-      <c r="G8" s="21">
-        <v>-36.6</v>
-      </c>
-      <c r="H8" s="24">
+      <c r="F8" s="28">
+        <v>-28.2</v>
+      </c>
+      <c r="G8" s="27">
+        <v>-37.799999999999997</v>
+      </c>
+      <c r="H8" s="31">
         <f t="shared" si="0"/>
-        <v>-9.4000000000000021</v>
-      </c>
-      <c r="I8" s="23"/>
+        <v>-9.5999999999999979</v>
+      </c>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
@@ -1299,17 +1376,17 @@
       <c r="E9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="27">
         <v>-3.3</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="30">
         <v>-0.7</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="31">
         <f t="shared" si="0"/>
         <v>2.5999999999999996</v>
       </c>
-      <c r="I9" s="23"/>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
@@ -1324,17 +1401,17 @@
       <c r="E10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="28">
         <v>-50.2</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="27">
         <v>-51.5</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="31">
         <f t="shared" si="0"/>
         <v>-1.2999999999999972</v>
       </c>
-      <c r="I10" s="23"/>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
@@ -1349,17 +1426,17 @@
       <c r="E11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="21">
-        <v>-3.7</v>
-      </c>
-      <c r="G11" s="22">
-        <v>-3.2</v>
-      </c>
-      <c r="H11" s="24">
+      <c r="F11" s="27">
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="G11" s="28">
+        <v>-4</v>
+      </c>
+      <c r="H11" s="31">
         <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="I11" s="23"/>
+        <v>0.90000000000000036</v>
+      </c>
+      <c r="I11" s="16"/>
     </row>
     <row r="12" spans="1:9" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="11">
@@ -1368,9 +1445,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="7">
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/气象/表格文件/比冷权重.xlsx
+++ b/气象/表格文件/比冷权重.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D80A994-CFA0-409B-8409-59611A64D0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6730265-3401-459C-AE7F-0DD87B9A4F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{61358E34-2C71-424E-88ED-402A34315EC4}"/>
   </bookViews>
@@ -332,10 +332,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>卡丘格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A的
 单项领先</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -346,8 +342,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>车臣乌拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>常年:
-1961-1990</t>
+2006-2025</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -779,6 +779,39 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="177" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="177" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -798,43 +831,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="177" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="177" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="177" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1178,38 +1178,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="19"/>
-      <c r="E1" s="35" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="30"/>
+      <c r="E1" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="26" t="s">
         <v>24</v>
-      </c>
-      <c r="I1" s="33" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="22"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="34"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="33"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
@@ -1221,21 +1221,21 @@
       <c r="C3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="25" t="s">
+      <c r="F3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="26" t="s">
+      <c r="G3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="24">
         <f xml:space="preserve"> B4*H4 + B5*H5 + B6*H6 + B7*H7 + B8*H8 + B9*H9 + B10*H10 + B11*H11</f>
-        <v>-0.4199999999999996</v>
+        <v>-0.75000000000000133</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
@@ -1251,15 +1251,15 @@
       <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="27">
-        <v>-29.4</v>
-      </c>
-      <c r="G4" s="28">
+      <c r="F4" s="19">
         <v>-28.4</v>
       </c>
-      <c r="H4" s="31">
+      <c r="G4" s="20">
+        <v>-28.3</v>
+      </c>
+      <c r="H4" s="23">
         <f>G4-F4</f>
-        <v>1</v>
+        <v>9.9999999999997868E-2</v>
       </c>
       <c r="I4" s="16"/>
     </row>
@@ -1276,15 +1276,15 @@
       <c r="E5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="29">
-        <v>-44.8</v>
-      </c>
-      <c r="G5" s="27">
-        <v>-44.5</v>
-      </c>
-      <c r="H5" s="31">
+      <c r="F5" s="21">
+        <v>-45</v>
+      </c>
+      <c r="G5" s="19">
+        <v>-46.2</v>
+      </c>
+      <c r="H5" s="23">
         <f t="shared" ref="H5:H11" si="0">G5-F5</f>
-        <v>0.29999999999999716</v>
+        <v>-1.2000000000000028</v>
       </c>
       <c r="I5" s="16"/>
     </row>
@@ -1301,15 +1301,15 @@
       <c r="E6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="21">
         <v>-36</v>
       </c>
-      <c r="G6" s="27">
-        <v>-36.299999999999997</v>
-      </c>
-      <c r="H6" s="31">
+      <c r="G6" s="19">
+        <v>-36.9</v>
+      </c>
+      <c r="H6" s="23">
         <f t="shared" si="0"/>
-        <v>-0.29999999999999716</v>
+        <v>-0.89999999999999858</v>
       </c>
       <c r="I6" s="16"/>
     </row>
@@ -1326,15 +1326,15 @@
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="27">
-        <v>-27.1</v>
-      </c>
-      <c r="G7" s="28">
+      <c r="F7" s="20">
         <v>-26</v>
       </c>
-      <c r="H7" s="31">
+      <c r="G7" s="19">
+        <v>-26.1</v>
+      </c>
+      <c r="H7" s="23">
         <f t="shared" si="0"/>
-        <v>1.1000000000000014</v>
+        <v>-0.10000000000000142</v>
       </c>
       <c r="I7" s="16"/>
     </row>
@@ -1351,15 +1351,15 @@
       <c r="E8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="28">
-        <v>-28.2</v>
-      </c>
-      <c r="G8" s="27">
-        <v>-37.799999999999997</v>
-      </c>
-      <c r="H8" s="31">
+      <c r="F8" s="20">
+        <v>-27.9</v>
+      </c>
+      <c r="G8" s="19">
+        <v>-31.8</v>
+      </c>
+      <c r="H8" s="23">
         <f t="shared" si="0"/>
-        <v>-9.5999999999999979</v>
+        <v>-3.9000000000000021</v>
       </c>
       <c r="I8" s="16"/>
     </row>
@@ -1376,15 +1376,15 @@
       <c r="E9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="19">
         <v>-3.3</v>
       </c>
-      <c r="G9" s="30">
-        <v>-0.7</v>
-      </c>
-      <c r="H9" s="31">
+      <c r="G9" s="22">
+        <v>2.6</v>
+      </c>
+      <c r="H9" s="23">
         <f t="shared" si="0"/>
-        <v>2.5999999999999996</v>
+        <v>5.9</v>
       </c>
       <c r="I9" s="16"/>
     </row>
@@ -1401,15 +1401,15 @@
       <c r="E10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="20">
         <v>-50.2</v>
       </c>
-      <c r="G10" s="27">
-        <v>-51.5</v>
-      </c>
-      <c r="H10" s="31">
+      <c r="G10" s="19">
+        <v>-54.7</v>
+      </c>
+      <c r="H10" s="23">
         <f t="shared" si="0"/>
-        <v>-1.2999999999999972</v>
+        <v>-4.5</v>
       </c>
       <c r="I10" s="16"/>
     </row>
@@ -1426,15 +1426,15 @@
       <c r="E11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="20">
+        <v>-3.6</v>
+      </c>
+      <c r="G11" s="19">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="G11" s="28">
-        <v>-4</v>
-      </c>
-      <c r="H11" s="31">
+      <c r="H11" s="23">
         <f t="shared" si="0"/>
-        <v>0.90000000000000036</v>
+        <v>-1.3000000000000003</v>
       </c>
       <c r="I11" s="16"/>
     </row>

--- a/气象/表格文件/比冷权重.xlsx
+++ b/气象/表格文件/比冷权重.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6730265-3401-459C-AE7F-0DD87B9A4F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980F39F8-274A-4ACB-AF71-F8CEE3DAB616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{61358E34-2C71-424E-88ED-402A34315EC4}"/>
   </bookViews>
@@ -236,10 +236,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>图里河</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -342,12 +338,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>车臣乌拉</t>
+    <t>East Grip</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥伊米亚康</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>常年:
-2006-2025</t>
+14/15~25/26</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -359,7 +359,7 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -548,33 +548,7 @@
     <font>
       <b/>
       <sz val="24"/>
-      <color rgb="FFFF00FF"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -591,6 +565,23 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FFFF00FF"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -727,7 +718,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -785,56 +776,53 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="4"/>
-    </xf>
     <xf numFmtId="177" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="4"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="4"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1178,38 +1166,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="30"/>
-      <c r="E1" s="34" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="28"/>
+      <c r="E1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="H1" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="I1" s="24" t="s">
         <v>23</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="33"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="31"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
@@ -1225,17 +1213,17 @@
         <v>3</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="24">
+        <v>19</v>
+      </c>
+      <c r="I3" s="21">
         <f xml:space="preserve"> B4*H4 + B5*H5 + B6*H6 + B7*H7 + B8*H8 + B9*H9 + B10*H10 + B11*H11</f>
-        <v>-0.75000000000000133</v>
+        <v>-0.65499999999999847</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
@@ -1251,15 +1239,15 @@
       <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="19">
-        <v>-28.4</v>
-      </c>
-      <c r="G4" s="20">
-        <v>-28.3</v>
-      </c>
-      <c r="H4" s="23">
+      <c r="F4" s="34">
+        <v>-45</v>
+      </c>
+      <c r="G4" s="22">
+        <v>-42.8</v>
+      </c>
+      <c r="H4" s="20">
         <f>G4-F4</f>
-        <v>9.9999999999997868E-2</v>
+        <v>2.2000000000000028</v>
       </c>
       <c r="I4" s="16"/>
     </row>
@@ -1276,21 +1264,21 @@
       <c r="E5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="21">
-        <v>-45</v>
-      </c>
-      <c r="G5" s="19">
-        <v>-46.2</v>
-      </c>
-      <c r="H5" s="23">
+      <c r="F5" s="22">
+        <v>-57.2</v>
+      </c>
+      <c r="G5" s="34">
+        <v>-62.9</v>
+      </c>
+      <c r="H5" s="20">
         <f t="shared" ref="H5:H11" si="0">G5-F5</f>
-        <v>-1.2000000000000028</v>
+        <v>-5.6999999999999957</v>
       </c>
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="14">
         <v>0.15</v>
@@ -1299,17 +1287,17 @@
         <v>0</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="21">
-        <v>-36</v>
-      </c>
-      <c r="G6" s="19">
-        <v>-36.9</v>
-      </c>
-      <c r="H6" s="23">
+        <v>18</v>
+      </c>
+      <c r="F6" s="34">
+        <v>-51.4</v>
+      </c>
+      <c r="G6" s="22">
+        <v>-48.3</v>
+      </c>
+      <c r="H6" s="20">
         <f t="shared" si="0"/>
-        <v>-0.89999999999999858</v>
+        <v>3.1000000000000014</v>
       </c>
       <c r="I6" s="16"/>
     </row>
@@ -1326,15 +1314,15 @@
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="20">
-        <v>-26</v>
-      </c>
-      <c r="G7" s="19">
-        <v>-26.1</v>
-      </c>
-      <c r="H7" s="23">
+      <c r="F7" s="34">
+        <v>-43.4</v>
+      </c>
+      <c r="G7" s="22">
+        <v>-41.7</v>
+      </c>
+      <c r="H7" s="20">
         <f t="shared" si="0"/>
-        <v>-0.10000000000000142</v>
+        <v>1.6999999999999957</v>
       </c>
       <c r="I7" s="16"/>
     </row>
@@ -1351,21 +1339,21 @@
       <c r="E8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="20">
-        <v>-27.9</v>
-      </c>
-      <c r="G8" s="19">
-        <v>-31.8</v>
-      </c>
-      <c r="H8" s="23">
+      <c r="F8" s="22">
+        <v>-53.1</v>
+      </c>
+      <c r="G8" s="34">
+        <v>-55.8</v>
+      </c>
+      <c r="H8" s="20">
         <f t="shared" si="0"/>
-        <v>-3.9000000000000021</v>
+        <v>-2.6999999999999957</v>
       </c>
       <c r="I8" s="16"/>
     </row>
     <row r="9" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="15">
         <v>0.05</v>
@@ -1374,17 +1362,17 @@
         <v>15</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="19">
-        <v>-3.3</v>
-      </c>
-      <c r="G9" s="22">
-        <v>2.6</v>
-      </c>
-      <c r="H9" s="23">
+        <v>17</v>
+      </c>
+      <c r="F9" s="34">
+        <v>-25.1</v>
+      </c>
+      <c r="G9" s="19">
+        <v>-14.2</v>
+      </c>
+      <c r="H9" s="20">
         <f t="shared" si="0"/>
-        <v>5.9</v>
+        <v>10.900000000000002</v>
       </c>
       <c r="I9" s="16"/>
     </row>
@@ -1401,15 +1389,15 @@
       <c r="E10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="20">
-        <v>-50.2</v>
-      </c>
-      <c r="G10" s="19">
-        <v>-54.7</v>
-      </c>
-      <c r="H10" s="23">
+      <c r="F10" s="22">
+        <v>-61</v>
+      </c>
+      <c r="G10" s="34">
+        <v>-67.5</v>
+      </c>
+      <c r="H10" s="20">
         <f t="shared" si="0"/>
-        <v>-4.5</v>
+        <v>-6.5</v>
       </c>
       <c r="I10" s="16"/>
     </row>
@@ -1426,15 +1414,15 @@
       <c r="E11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="20">
-        <v>-3.6</v>
-      </c>
-      <c r="G11" s="19">
-        <v>-4.9000000000000004</v>
-      </c>
-      <c r="H11" s="23">
+      <c r="F11" s="22">
+        <v>-14</v>
+      </c>
+      <c r="G11" s="34">
+        <v>-28.7</v>
+      </c>
+      <c r="H11" s="20">
         <f t="shared" si="0"/>
-        <v>-1.3000000000000003</v>
+        <v>-14.7</v>
       </c>
       <c r="I11" s="16"/>
     </row>

--- a/气象/表格文件/比冷权重.xlsx
+++ b/气象/表格文件/比冷权重.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980F39F8-274A-4ACB-AF71-F8CEE3DAB616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C62DA7-92C2-48FE-AB79-352943A20961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{61358E34-2C71-424E-88ED-402A34315EC4}"/>
   </bookViews>
@@ -338,16 +338,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>East Grip</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥伊米亚康</t>
+    <t>沈阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莫斯科</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>常年:
-14/15~25/26</t>
+1991~2020</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -359,7 +359,7 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,15 +573,6 @@
     <font>
       <b/>
       <sz val="24"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color rgb="FFFF00FF"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -718,7 +709,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -820,9 +811,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="4"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1213,17 +1201,17 @@
         <v>3</v>
       </c>
       <c r="F3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>25</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>24</v>
       </c>
       <c r="H3" s="18" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="21">
         <f xml:space="preserve"> B4*H4 + B5*H5 + B6*H6 + B7*H7 + B8*H8 + B9*H9 + B10*H10 + B11*H11</f>
-        <v>-0.65499999999999847</v>
+        <v>0.5539999999999996</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
@@ -1239,15 +1227,15 @@
       <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="34">
-        <v>-45</v>
+      <c r="F4" s="22">
+        <v>-11.4</v>
       </c>
       <c r="G4" s="22">
-        <v>-42.8</v>
+        <v>-6.2</v>
       </c>
       <c r="H4" s="20">
         <f>G4-F4</f>
-        <v>2.2000000000000028</v>
+        <v>5.2</v>
       </c>
       <c r="I4" s="16"/>
     </row>
@@ -1265,14 +1253,14 @@
         <v>7</v>
       </c>
       <c r="F5" s="22">
-        <v>-57.2</v>
-      </c>
-      <c r="G5" s="34">
-        <v>-62.9</v>
+        <v>-25.7</v>
+      </c>
+      <c r="G5" s="22">
+        <v>-24.72</v>
       </c>
       <c r="H5" s="20">
         <f t="shared" ref="H5:H11" si="0">G5-F5</f>
-        <v>-5.6999999999999957</v>
+        <v>0.98000000000000043</v>
       </c>
       <c r="I5" s="16"/>
     </row>
@@ -1289,15 +1277,15 @@
       <c r="E6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="34">
-        <v>-51.4</v>
+      <c r="F6" s="22">
+        <v>-18.399999999999999</v>
       </c>
       <c r="G6" s="22">
-        <v>-48.3</v>
+        <v>-21.6</v>
       </c>
       <c r="H6" s="20">
         <f t="shared" si="0"/>
-        <v>3.1000000000000014</v>
+        <v>-3.2000000000000028</v>
       </c>
       <c r="I6" s="16"/>
     </row>
@@ -1314,15 +1302,15 @@
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="34">
-        <v>-43.4</v>
+      <c r="F7" s="22">
+        <v>-8.6999999999999993</v>
       </c>
       <c r="G7" s="22">
-        <v>-41.7</v>
+        <v>-5.5</v>
       </c>
       <c r="H7" s="20">
         <f t="shared" si="0"/>
-        <v>1.6999999999999957</v>
+        <v>3.1999999999999993</v>
       </c>
       <c r="I7" s="16"/>
     </row>
@@ -1340,14 +1328,14 @@
         <v>12</v>
       </c>
       <c r="F8" s="22">
-        <v>-53.1</v>
-      </c>
-      <c r="G8" s="34">
-        <v>-55.8</v>
+        <v>-13.93</v>
+      </c>
+      <c r="G8" s="22">
+        <v>-17.7</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="0"/>
-        <v>-2.6999999999999957</v>
+        <v>-3.7699999999999996</v>
       </c>
       <c r="I8" s="16"/>
     </row>
@@ -1364,15 +1352,15 @@
       <c r="E9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="34">
-        <v>-25.1</v>
+      <c r="F9" s="22">
+        <v>8.6</v>
       </c>
       <c r="G9" s="19">
-        <v>-14.2</v>
+        <v>8.6</v>
       </c>
       <c r="H9" s="20">
         <f t="shared" si="0"/>
-        <v>10.900000000000002</v>
+        <v>0</v>
       </c>
       <c r="I9" s="16"/>
     </row>
@@ -1390,14 +1378,14 @@
         <v>8</v>
       </c>
       <c r="F10" s="22">
-        <v>-61</v>
-      </c>
-      <c r="G10" s="34">
-        <v>-67.5</v>
+        <v>-33.1</v>
+      </c>
+      <c r="G10" s="22">
+        <v>-42.1</v>
       </c>
       <c r="H10" s="20">
         <f t="shared" si="0"/>
-        <v>-6.5</v>
+        <v>-9</v>
       </c>
       <c r="I10" s="16"/>
     </row>
@@ -1415,14 +1403,14 @@
         <v>11</v>
       </c>
       <c r="F11" s="22">
-        <v>-14</v>
-      </c>
-      <c r="G11" s="34">
-        <v>-28.7</v>
+        <v>8.6</v>
+      </c>
+      <c r="G11" s="22">
+        <v>6.3</v>
       </c>
       <c r="H11" s="20">
         <f t="shared" si="0"/>
-        <v>-14.7</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="I11" s="16"/>
     </row>

--- a/气象/表格文件/比冷权重.xlsx
+++ b/气象/表格文件/比冷权重.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C62DA7-92C2-48FE-AB79-352943A20961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1AC914-544D-42B4-8613-8434CE32E6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{61358E34-2C71-424E-88ED-402A34315EC4}"/>
   </bookViews>
@@ -33,8 +33,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>爆发力</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -60,13 +82,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026-09-04 by @蒙古冷迷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>平均每冬</t>
-    </r>
+    <t>最冷月份平均气温</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年平均气温</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏冷
+持久性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -77,25 +105,26 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>最低</t>
+      <t>稳定性</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>气温</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>历史</t>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+持久性</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">昼温
+</t>
     </r>
     <r>
       <rPr>
@@ -107,93 +136,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>最低</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>气温</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最冷月份平均气温</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冬三月平均气温</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>年平均气温</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>平均每冬最低</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FFC00000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>昼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>温</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏冷
-持久性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF4361EE"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>稳定性</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-持久性</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -206,105 +149,141 @@
       <rPr>
         <b/>
         <sz val="16"/>
-        <color rgb="FF4361EE"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>稳定性</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">昼温
-</t>
+        <color rgb="FFF72585"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>爆发力</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Toko</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坚边奇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1991~2020
+一月平均气温</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1991~2020
+冬三月平均气温</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>历史极端冷冬
+冬三月平均气温</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>权重</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最冷月份
+历史最高气温</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>平均每冬</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="16"/>
-        <color rgb="FFF72585"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>爆发力</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
+        <color rgb="FF0070C0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>最低</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="16"/>
-        <color rgb="FFFF00FF"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>最冷月份</t>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>气温</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>平均每冬最低</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-历史</t>
-    </r>
+        <color rgb="FF0070C0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>昼温</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="16"/>
-        <color rgb="FFC00000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>最高</t>
+        <color rgb="FF0070C0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>冬三月</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>气温</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>平均气温</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>历史极端</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="16"/>
-        <color rgb="FFFF00FF"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>历史极端冷月</t>
+        <color rgb="FF0070C0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>冷月</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="16"/>
-        <color theme="1"/>
         <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
@@ -316,38 +295,203 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>差值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A的
-单项领先</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A的加权
-综合领先</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>沈阳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莫斯科</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>常年:
-1991~2020</t>
+    <t>1991~2020
+年平均气温</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最冷月份
+平均气温</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>历史极端</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>冷月</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+平均气温</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">冬三月
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>平均气温</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>平均
+每冬最低</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>昼温</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>平均
+每冬</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>最低</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>气温</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>历史最低</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>气温</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>历史最低</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>气温</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高阶寒冷PK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">常年: 1961~1990
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>极值不受年份限制</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>综合得分
+(相对0的优势分)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PK净胜总分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -355,11 +499,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="178" formatCode="0.000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,6 +531,154 @@
     </font>
     <font>
       <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FFFFFF00"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF4361EE"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFF72585"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="32"/>
+      <color rgb="FFF72585"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="32"/>
+      <color rgb="FFB5179E"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="32"/>
+      <color rgb="FF7209B7"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="32"/>
+      <color rgb="FF4361EE"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF0070C0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FF0070C0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -396,16 +689,23 @@
     <font>
       <b/>
       <sz val="20"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color rgb="FFFFFF00"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF0070C0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="0"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -422,25 +722,16 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FF4361EE"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFC00000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
+      <sz val="12"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
       <color rgb="FFF72585"/>
       <name val="等线"/>
       <family val="3"/>
@@ -449,15 +740,7 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="36"/>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
@@ -466,104 +749,7 @@
     </font>
     <font>
       <b/>
-      <sz val="32"/>
-      <color rgb="FFF72585"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="32"/>
-      <color rgb="FFB5179E"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="32"/>
-      <color rgb="FF7209B7"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="32"/>
-      <color rgb="FF4361EE"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFF00FF"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF3F37C9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF3F37C9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="0" tint="-0.249977111117893"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="24"/>
-      <color theme="1" tint="0.499984740745262"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="3"/>
@@ -572,14 +758,15 @@
     </font>
     <font>
       <b/>
-      <sz val="24"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -604,8 +791,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -676,10 +869,80 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,18 +951,18 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="0"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color theme="1"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -709,7 +972,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -719,98 +982,158 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="18" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -820,10 +1143,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF72585"/>
       <color rgb="FFFF00FF"/>
       <color rgb="FF3F37C9"/>
       <color rgb="FF7209B7"/>
-      <color rgb="FFF72585"/>
       <color rgb="FF4361EE"/>
       <color rgb="FF3A0CA3"/>
       <color rgb="FF480CA8"/>
@@ -1140,295 +1463,361 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F945DB-23E0-4275-8605-818D25F42E67}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.59765625" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.06640625" style="1"/>
-    <col min="5" max="7" width="24.59765625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.59765625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.59765625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.06640625" style="1"/>
+    <col min="3" max="4" width="14.59765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.59765625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="20.59765625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.8">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E1" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="44">
+        <f xml:space="preserve"> $B4*(-F4) + $B5*(-F5) + $B6*(-F6) + $B7*(-F7) + $B8*(-F8) + $B9*(-F9) + $B10*(-F10) + $B11*(-F11)</f>
+        <v>41.24</v>
+      </c>
+      <c r="G1" s="44">
+        <f xml:space="preserve"> $B4*(-G4) + $B5*(-G5) + $B6*(-G6) + $B7*(-G7) + $B8*(-G8) + $B9*(-G9) + $B10*(-G10) + $B11*(-G11)</f>
+        <v>42.214999999999996</v>
+      </c>
+      <c r="H1" s="43">
+        <f>SUM(H4:H11)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="28"/>
-      <c r="E1" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="31"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="51"/>
+      <c r="H2" s="52"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="42"/>
+      <c r="E3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="37"/>
+      <c r="E4" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F4" s="20">
+        <v>-38.799999999999997</v>
+      </c>
+      <c r="G4" s="21">
+        <v>-38.1</v>
+      </c>
+      <c r="H4" s="18">
+        <f>B4</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="38"/>
+      <c r="E5" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="28">
+        <v>-54.6</v>
+      </c>
+      <c r="G5" s="29">
+        <v>-55.8</v>
+      </c>
+      <c r="H5" s="30">
+        <f t="shared" ref="H5:H11" si="0">B5</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="39"/>
+      <c r="E6" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="21">
-        <f xml:space="preserve"> B4*H4 + B5*H5 + B6*H6 + B7*H7 + B8*H8 + B9*H9 + B10*H10 + B11*H11</f>
-        <v>0.5539999999999996</v>
+      <c r="F6" s="22">
+        <v>-46.6</v>
+      </c>
+      <c r="G6" s="23">
+        <v>-48.4</v>
+      </c>
+      <c r="H6" s="19">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4" t="s">
+    <row r="7" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="22">
-        <v>-11.4</v>
-      </c>
-      <c r="G4" s="22">
-        <v>-6.2</v>
-      </c>
-      <c r="H4" s="20">
-        <f>G4-F4</f>
-        <v>5.2</v>
-      </c>
-      <c r="I4" s="16"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="29">
+        <v>-36.700000000000003</v>
+      </c>
+      <c r="G7" s="28">
+        <v>-35.700000000000003</v>
+      </c>
+      <c r="H7" s="30">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4" t="s">
+    <row r="8" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="40"/>
+      <c r="E8" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="22">
+        <v>-42</v>
+      </c>
+      <c r="G8" s="23">
+        <v>-51.3</v>
+      </c>
+      <c r="H8" s="19">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="40"/>
+      <c r="E9" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="29">
+        <v>-6.3</v>
+      </c>
+      <c r="G9" s="31">
+        <v>-4.7</v>
+      </c>
+      <c r="H9" s="30">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="38"/>
+      <c r="E10" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="23">
+        <v>-61.1</v>
+      </c>
+      <c r="G10" s="22">
+        <v>-60</v>
+      </c>
+      <c r="H10" s="19">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="B11" s="11">
+        <v>0.05</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="40"/>
+      <c r="E11" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="22">
-        <v>-25.7</v>
-      </c>
-      <c r="G5" s="22">
-        <v>-24.72</v>
-      </c>
-      <c r="H5" s="20">
-        <f t="shared" ref="H5:H11" si="0">G5-F5</f>
-        <v>0.98000000000000043</v>
-      </c>
-      <c r="I5" s="16"/>
+      <c r="F11" s="29">
+        <v>-11.1</v>
+      </c>
+      <c r="G11" s="28">
+        <v>-11</v>
+      </c>
+      <c r="H11" s="30">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="14">
-        <v>0.15</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="22">
-        <v>-18.399999999999999</v>
-      </c>
-      <c r="G6" s="22">
-        <v>-21.6</v>
-      </c>
-      <c r="H6" s="20">
-        <f t="shared" si="0"/>
-        <v>-3.2000000000000028</v>
-      </c>
-      <c r="I6" s="16"/>
-    </row>
-    <row r="7" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="14">
-        <v>0.15</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="22">
-        <v>-8.6999999999999993</v>
-      </c>
-      <c r="G7" s="22">
-        <v>-5.5</v>
-      </c>
-      <c r="H7" s="20">
-        <f t="shared" si="0"/>
-        <v>3.1999999999999993</v>
-      </c>
-      <c r="I7" s="16"/>
-    </row>
-    <row r="8" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="14">
-        <v>0.1</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="22">
-        <v>-13.93</v>
-      </c>
-      <c r="G8" s="22">
-        <v>-17.7</v>
-      </c>
-      <c r="H8" s="20">
-        <f t="shared" si="0"/>
-        <v>-3.7699999999999996</v>
-      </c>
-      <c r="I8" s="16"/>
-    </row>
-    <row r="9" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="15">
-        <v>0.05</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="22">
-        <v>8.6</v>
-      </c>
-      <c r="G9" s="19">
-        <v>8.6</v>
-      </c>
-      <c r="H9" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="16"/>
-    </row>
-    <row r="10" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="15">
-        <v>0.05</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="22">
-        <v>-33.1</v>
-      </c>
-      <c r="G10" s="22">
-        <v>-42.1</v>
-      </c>
-      <c r="H10" s="20">
-        <f t="shared" si="0"/>
-        <v>-9</v>
-      </c>
-      <c r="I10" s="16"/>
-    </row>
-    <row r="11" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="15">
-        <v>0.05</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="22">
-        <v>8.6</v>
-      </c>
-      <c r="G11" s="22">
-        <v>6.3</v>
-      </c>
-      <c r="H11" s="20">
-        <f t="shared" si="0"/>
-        <v>-2.2999999999999998</v>
-      </c>
-      <c r="I11" s="16"/>
-    </row>
-    <row r="12" spans="1:9" ht="44" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="11">
+    <row r="12" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="7">
         <f>SUM(B4:B11)</f>
         <v>1</v>
       </c>
+      <c r="E12" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="47" t="str" cm="1">
+        <f t="array" ref="F12" xml:space="preserve"> _xlfn.IFS( F1&gt;G1, F1-G1, F1&lt;G1, "败方", F1=G1, "平局" )</f>
+        <v>败方</v>
+      </c>
+      <c r="G12" s="45" cm="1">
+        <f t="array" ref="G12" xml:space="preserve"> _xlfn.IFS( F1&lt;G1, G1-F1, F1&gt;G1, "败方", F1=G1, "平局" )</f>
+        <v>0.97499999999999432</v>
+      </c>
+      <c r="H12" s="34">
+        <f>SUM(H4:H11)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="32">
+        <v>-41.3</v>
+      </c>
+      <c r="G13" s="23">
+        <v>-45.7</v>
+      </c>
+      <c r="H13" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E14" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="23">
+        <v>-36.6</v>
+      </c>
+      <c r="G14" s="32">
+        <v>-36.5</v>
+      </c>
+      <c r="H14" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E15" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="23">
+        <v>-34.9</v>
+      </c>
+      <c r="G15" s="32">
+        <v>-34.5</v>
+      </c>
+      <c r="H15" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="44" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="23">
+        <v>-9.9</v>
+      </c>
+      <c r="G16" s="32">
+        <v>-9.6</v>
+      </c>
+      <c r="H16" s="19">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A1:C1"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="F3:G16 E2" name="区域2"/>
+  </protectedRanges>
+  <mergeCells count="2">
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/气象/表格文件/比冷权重.xlsx
+++ b/气象/表格文件/比冷权重.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1AC914-544D-42B4-8613-8434CE32E6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F326BCE6-C89E-44B9-ACC5-1E14777E3B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{61358E34-2C71-424E-88ED-402A34315EC4}"/>
   </bookViews>
@@ -160,14 +160,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Toko</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坚边奇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1991~2020
 一月平均气温</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -467,8 +459,25 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">常年: 1961~1990
+    <t>综合得分
+(相对0的优势分)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PK净胜总分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈尔滨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿勒泰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">常年: 1991~2020
 </t>
     </r>
     <r>
@@ -483,15 +492,6 @@
       </rPr>
       <t>极值不受年份限制</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>综合得分
-(相对0的优势分)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PK净胜总分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,7 +504,7 @@
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="0.000"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -624,22 +624,6 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -654,15 +638,6 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF0070C0"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
       <color rgb="FF0070C0"/>
       <name val="等线"/>
       <family val="3"/>
@@ -972,7 +947,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1021,67 +996,52 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="177" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="18" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="177" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="23" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="20" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1102,20 +1062,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1126,20 +1089,58 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0070C0"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -1476,37 +1477,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="E1" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="44">
+      <c r="E1" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="39">
         <f xml:space="preserve"> $B4*(-F4) + $B5*(-F5) + $B6*(-F6) + $B7*(-F7) + $B8*(-F8) + $B9*(-F9) + $B10*(-F10) + $B11*(-F11)</f>
-        <v>41.24</v>
-      </c>
-      <c r="G1" s="44">
+        <v>20.079999000000001</v>
+      </c>
+      <c r="G1" s="39">
         <f xml:space="preserve"> $B4*(-G4) + $B5*(-G5) + $B6*(-G6) + $B7*(-G7) + $B8*(-G8) + $B9*(-G9) + $B10*(-G10) + $B11*(-G11)</f>
-        <v>42.214999999999996</v>
-      </c>
-      <c r="H1" s="43">
+        <v>20.400166500000005</v>
+      </c>
+      <c r="H1" s="38">
         <f>SUM(H4:H11)</f>
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="52"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="47"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
@@ -1518,18 +1519,18 @@
       <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="42"/>
+      <c r="D3" s="37"/>
       <c r="E3" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="36" t="s">
-        <v>13</v>
+      <c r="F3" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>33</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I3" s="15"/>
     </row>
@@ -1543,15 +1544,15 @@
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="24" t="s">
-        <v>24</v>
+      <c r="D4" s="32"/>
+      <c r="E4" s="22" t="s">
+        <v>22</v>
       </c>
       <c r="F4" s="20">
-        <v>-38.799999999999997</v>
-      </c>
-      <c r="G4" s="21">
-        <v>-38.1</v>
+        <v>-17.273330000000001</v>
+      </c>
+      <c r="G4" s="20">
+        <v>-15.82</v>
       </c>
       <c r="H4" s="18">
         <f>B4</f>
@@ -1560,7 +1561,7 @@
     </row>
     <row r="5" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="9">
         <v>0.2</v>
@@ -1568,24 +1569,24 @@
       <c r="C5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="28">
-        <v>-54.6</v>
-      </c>
-      <c r="G5" s="29">
-        <v>-55.8</v>
-      </c>
-      <c r="H5" s="30">
+      <c r="D5" s="33"/>
+      <c r="E5" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="26">
+        <v>-29.42</v>
+      </c>
+      <c r="G5" s="26">
+        <v>-33.74</v>
+      </c>
+      <c r="H5" s="27">
         <f t="shared" ref="H5:H11" si="0">B5</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="10">
         <v>0.15</v>
@@ -1593,15 +1594,15 @@
       <c r="C6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="22">
-        <v>-46.6</v>
-      </c>
-      <c r="G6" s="23">
-        <v>-48.4</v>
+      <c r="D6" s="34"/>
+      <c r="E6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="20">
+        <v>-27.5</v>
+      </c>
+      <c r="G6" s="20">
+        <v>-25.1</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="0"/>
@@ -1610,7 +1611,7 @@
     </row>
     <row r="7" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" s="10">
         <v>0.15</v>
@@ -1618,24 +1619,24 @@
       <c r="C7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="40"/>
-      <c r="E7" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="29">
-        <v>-36.700000000000003</v>
-      </c>
-      <c r="G7" s="28">
-        <v>-35.700000000000003</v>
-      </c>
-      <c r="H7" s="30">
+      <c r="D7" s="35"/>
+      <c r="E7" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="26">
+        <v>-14.55</v>
+      </c>
+      <c r="G7" s="26">
+        <v>-13.61</v>
+      </c>
+      <c r="H7" s="27">
         <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" s="10">
         <v>0.1</v>
@@ -1643,15 +1644,15 @@
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="40"/>
-      <c r="E8" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="22">
-        <v>-42</v>
-      </c>
-      <c r="G8" s="23">
-        <v>-51.3</v>
+      <c r="D8" s="35"/>
+      <c r="E8" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="20">
+        <v>-19.690000000000001</v>
+      </c>
+      <c r="G8" s="20">
+        <v>-22.28</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="0"/>
@@ -1660,7 +1661,7 @@
     </row>
     <row r="9" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="11">
         <v>0.05</v>
@@ -1668,24 +1669,24 @@
       <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="40"/>
-      <c r="E9" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="29">
-        <v>-6.3</v>
-      </c>
-      <c r="G9" s="31">
-        <v>-4.7</v>
-      </c>
-      <c r="H9" s="30">
+      <c r="D9" s="35"/>
+      <c r="E9" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="26">
+        <v>4.2</v>
+      </c>
+      <c r="G9" s="26">
+        <v>5.3</v>
+      </c>
+      <c r="H9" s="27">
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="50" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" s="11">
         <v>0.05</v>
@@ -1693,15 +1694,15 @@
       <c r="C10" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="38"/>
-      <c r="E10" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="23">
-        <v>-61.1</v>
-      </c>
-      <c r="G10" s="22">
-        <v>-60</v>
+      <c r="D10" s="33"/>
+      <c r="E10" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="20">
+        <v>-41.4</v>
+      </c>
+      <c r="G10" s="20">
+        <v>-43.5</v>
       </c>
       <c r="H10" s="19">
         <f t="shared" si="0"/>
@@ -1718,17 +1719,17 @@
       <c r="C11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="40"/>
-      <c r="E11" s="27" t="s">
+      <c r="D11" s="35"/>
+      <c r="E11" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="29">
-        <v>-11.1</v>
-      </c>
-      <c r="G11" s="28">
-        <v>-11</v>
-      </c>
-      <c r="H11" s="30">
+      <c r="F11" s="26">
+        <v>5.1766699999999997</v>
+      </c>
+      <c r="G11" s="26">
+        <v>4.9466700000000001</v>
+      </c>
+      <c r="H11" s="27">
         <f t="shared" si="0"/>
         <v>0.05</v>
       </c>
@@ -1738,30 +1739,30 @@
         <f>SUM(B4:B11)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="47" t="str" cm="1">
+      <c r="E12" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="42" t="str" cm="1">
         <f t="array" ref="F12" xml:space="preserve"> _xlfn.IFS( F1&gt;G1, F1-G1, F1&lt;G1, "败方", F1=G1, "平局" )</f>
         <v>败方</v>
       </c>
-      <c r="G12" s="45" cm="1">
+      <c r="G12" s="40" cm="1">
         <f t="array" ref="G12" xml:space="preserve"> _xlfn.IFS( F1&lt;G1, G1-F1, F1&gt;G1, "败方", F1=G1, "平局" )</f>
-        <v>0.97499999999999432</v>
-      </c>
-      <c r="H12" s="34">
+        <v>0.32016750000000371</v>
+      </c>
+      <c r="H12" s="29">
         <f>SUM(H4:H11)</f>
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E13" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="32">
+        <v>14</v>
+      </c>
+      <c r="F13" s="21">
         <v>-41.3</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="21">
         <v>-45.7</v>
       </c>
       <c r="H13" s="19">
@@ -1770,12 +1771,12 @@
     </row>
     <row r="14" spans="1:9" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E14" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="23">
+        <v>12</v>
+      </c>
+      <c r="F14" s="21">
         <v>-36.6</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="21">
         <v>-36.5</v>
       </c>
       <c r="H14" s="19">
@@ -1784,12 +1785,12 @@
     </row>
     <row r="15" spans="1:9" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E15" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="23">
+        <v>13</v>
+      </c>
+      <c r="F15" s="21">
         <v>-34.9</v>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="21">
         <v>-34.5</v>
       </c>
       <c r="H15" s="19">
@@ -1798,12 +1799,12 @@
     </row>
     <row r="16" spans="1:9" ht="44" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="23">
+        <v>21</v>
+      </c>
+      <c r="F16" s="21">
         <v>-9.9</v>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="21">
         <v>-9.6</v>
       </c>
       <c r="H16" s="19">
@@ -1813,13 +1814,38 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="F3:G16 E2" name="区域2"/>
+    <protectedRange sqref="F3:G16 E2" name="区域1"/>
   </protectedRanges>
   <mergeCells count="2">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="F2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="F4:G4">
+    <cfRule type="aboveAverage" dxfId="7" priority="10" aboveAverage="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:G5">
+    <cfRule type="aboveAverage" dxfId="6" priority="6" aboveAverage="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:G6">
+    <cfRule type="aboveAverage" dxfId="5" priority="9" aboveAverage="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:G7">
+    <cfRule type="aboveAverage" dxfId="4" priority="5" aboveAverage="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:G8">
+    <cfRule type="aboveAverage" dxfId="3" priority="8" aboveAverage="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9:G9">
+    <cfRule type="aboveAverage" dxfId="2" priority="4" aboveAverage="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10:G10">
+    <cfRule type="aboveAverage" dxfId="1" priority="7" aboveAverage="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11:G11">
+    <cfRule type="aboveAverage" dxfId="0" priority="3" aboveAverage="0"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/气象/表格文件/比冷权重.xlsx
+++ b/气象/表格文件/比冷权重.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\表格文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F326BCE6-C89E-44B9-ACC5-1E14777E3B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4ECF68-2D15-457C-A1E3-0215C5279936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{61358E34-2C71-424E-88ED-402A34315EC4}"/>
   </bookViews>
@@ -468,11 +468,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>哈尔滨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿勒泰</t>
+    <t>Toko</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -492,6 +488,10 @@
       </rPr>
       <t>极值不受年份限制</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊利尔涅伊</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,7 +504,7 @@
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="0.000"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -735,6 +735,15 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="0"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1041,9 +1050,6 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1068,18 +1074,18 @@
     <xf numFmtId="2" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
     <xf numFmtId="178" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1094,6 +1100,9 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1477,37 +1486,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="39">
+      <c r="F1" s="38">
         <f xml:space="preserve"> $B4*(-F4) + $B5*(-F5) + $B6*(-F6) + $B7*(-F7) + $B8*(-F8) + $B9*(-F9) + $B10*(-F10) + $B11*(-F11)</f>
-        <v>20.079999000000001</v>
-      </c>
-      <c r="G1" s="39">
+        <v>39.7575</v>
+      </c>
+      <c r="G1" s="38">
         <f xml:space="preserve"> $B4*(-G4) + $B5*(-G5) + $B6*(-G6) + $B7*(-G7) + $B8*(-G8) + $B9*(-G9) + $B10*(-G10) + $B11*(-G11)</f>
-        <v>20.400166500000005</v>
-      </c>
-      <c r="H1" s="38">
+        <v>39.736499999999999</v>
+      </c>
+      <c r="H1" s="37">
         <f>SUM(H4:H11)</f>
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="47" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="48"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
@@ -1519,15 +1528,15 @@
       <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="37"/>
+      <c r="D3" s="36"/>
       <c r="E3" s="16" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="31" t="s">
-        <v>33</v>
+      <c r="G3" s="48" t="s">
+        <v>34</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>15</v>
@@ -1544,15 +1553,15 @@
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="32"/>
+      <c r="D4" s="31"/>
       <c r="E4" s="22" t="s">
         <v>22</v>
       </c>
       <c r="F4" s="20">
-        <v>-17.273330000000001</v>
+        <v>-36.6</v>
       </c>
       <c r="G4" s="20">
-        <v>-15.82</v>
+        <v>-34.82</v>
       </c>
       <c r="H4" s="18">
         <f>B4</f>
@@ -1569,15 +1578,15 @@
       <c r="C5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="33"/>
+      <c r="D5" s="32"/>
       <c r="E5" s="25" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="26">
-        <v>-29.42</v>
+        <v>-53.1</v>
       </c>
       <c r="G5" s="26">
-        <v>-33.74</v>
+        <v>-53.04</v>
       </c>
       <c r="H5" s="27">
         <f t="shared" ref="H5:H11" si="0">B5</f>
@@ -1594,15 +1603,15 @@
       <c r="C6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="34"/>
+      <c r="D6" s="33"/>
       <c r="E6" s="23" t="s">
         <v>23</v>
       </c>
       <c r="F6" s="20">
-        <v>-27.5</v>
+        <v>-46.6</v>
       </c>
       <c r="G6" s="20">
-        <v>-25.1</v>
+        <v>-45.6</v>
       </c>
       <c r="H6" s="19">
         <f t="shared" si="0"/>
@@ -1619,15 +1628,15 @@
       <c r="C7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="35"/>
+      <c r="D7" s="34"/>
       <c r="E7" s="25" t="s">
         <v>24</v>
       </c>
       <c r="F7" s="26">
-        <v>-14.55</v>
+        <v>-34.89</v>
       </c>
       <c r="G7" s="26">
-        <v>-13.61</v>
+        <v>-33.65</v>
       </c>
       <c r="H7" s="27">
         <f t="shared" si="0"/>
@@ -1644,15 +1653,15 @@
       <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="34"/>
       <c r="E8" s="23" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="20">
-        <v>-19.690000000000001</v>
+        <v>-38.99</v>
       </c>
       <c r="G8" s="20">
-        <v>-22.28</v>
+        <v>-48.37</v>
       </c>
       <c r="H8" s="19">
         <f t="shared" si="0"/>
@@ -1669,15 +1678,15 @@
       <c r="C9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="35"/>
+      <c r="D9" s="34"/>
       <c r="E9" s="25" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="26">
-        <v>4.2</v>
+        <v>-6.3</v>
       </c>
       <c r="G9" s="26">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="H9" s="27">
         <f t="shared" si="0"/>
@@ -1694,15 +1703,15 @@
       <c r="C10" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D10" s="33"/>
+      <c r="D10" s="32"/>
       <c r="E10" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F10" s="20">
-        <v>-41.4</v>
+        <v>-61.1</v>
       </c>
       <c r="G10" s="20">
-        <v>-43.5</v>
+        <v>-64.400000000000006</v>
       </c>
       <c r="H10" s="19">
         <f t="shared" si="0"/>
@@ -1719,15 +1728,15 @@
       <c r="C11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="35"/>
+      <c r="D11" s="34"/>
       <c r="E11" s="25" t="s">
         <v>7</v>
       </c>
       <c r="F11" s="26">
-        <v>5.1766699999999997</v>
+        <v>-9.9</v>
       </c>
       <c r="G11" s="26">
-        <v>4.9466700000000001</v>
+        <v>-11.98</v>
       </c>
       <c r="H11" s="27">
         <f t="shared" si="0"/>
@@ -1742,13 +1751,13 @@
       <c r="E12" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="42" t="str" cm="1">
+      <c r="F12" s="41" cm="1">
         <f t="array" ref="F12" xml:space="preserve"> _xlfn.IFS( F1&gt;G1, F1-G1, F1&lt;G1, "败方", F1=G1, "平局" )</f>
+        <v>2.1000000000000796E-2</v>
+      </c>
+      <c r="G12" s="42" t="str" cm="1">
+        <f t="array" ref="G12" xml:space="preserve"> _xlfn.IFS( F1&lt;G1, G1-F1, F1&gt;G1, "败方", F1=G1, "平局" )</f>
         <v>败方</v>
-      </c>
-      <c r="G12" s="40" cm="1">
-        <f t="array" ref="G12" xml:space="preserve"> _xlfn.IFS( F1&lt;G1, G1-F1, F1&gt;G1, "败方", F1=G1, "平局" )</f>
-        <v>0.32016750000000371</v>
       </c>
       <c r="H12" s="29">
         <f>SUM(H4:H11)</f>
@@ -1760,10 +1769,10 @@
         <v>14</v>
       </c>
       <c r="F13" s="21">
-        <v>-41.3</v>
+        <v>-41.33</v>
       </c>
       <c r="G13" s="21">
-        <v>-45.7</v>
+        <v>-38.799999999999997</v>
       </c>
       <c r="H13" s="19">
         <v>0</v>
@@ -1773,12 +1782,8 @@
       <c r="E14" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="21">
-        <v>-36.6</v>
-      </c>
-      <c r="G14" s="21">
-        <v>-36.5</v>
-      </c>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
       <c r="H14" s="19">
         <v>0</v>
       </c>
@@ -1787,12 +1792,8 @@
       <c r="E15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="21">
-        <v>-34.9</v>
-      </c>
-      <c r="G15" s="21">
-        <v>-34.5</v>
-      </c>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
       <c r="H15" s="19">
         <v>0</v>
       </c>
@@ -1801,12 +1802,8 @@
       <c r="E16" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="21">
-        <v>-9.9</v>
-      </c>
-      <c r="G16" s="21">
-        <v>-9.6</v>
-      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
       <c r="H16" s="19">
         <v>0</v>
       </c>
